--- a/docs/QuickCart_Manual_Test_Cases.xlsx
+++ b/docs/QuickCart_Manual_Test_Cases.xlsx
@@ -1111,15 +1111,19 @@
           <t>Error "name must be 2 to 50 characters"; nothing is created (API 400).</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Registration page showed 'name must be 2 to 50 characters'; still on /register: True. Screenshot: test-results/manual/TC-M-004.png.</t>
+        </is>
+      </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-AUTH-04)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-AUTH-04</t>
         </is>
       </c>
     </row>
@@ -1168,15 +1172,19 @@
           <t>Error "name must be 2 to 50 characters" (API 400).</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Registration page showed 'name must be 2 to 50 characters'; still on /register: True. Screenshot: test-results/manual/TC-M-005.png.</t>
+        </is>
+      </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-AUTH-06)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-AUTH-06</t>
         </is>
       </c>
     </row>
@@ -1286,15 +1294,19 @@
           <t>Error "password must be 6 to 20 characters" (API 400).</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Registration page showed 'password must be 6 to 20 characters'; still on /register: True. Screenshot: test-results/manual/TC-M-007.png.</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-AUTH-10)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-AUTH-10</t>
         </is>
       </c>
     </row>
@@ -1819,15 +1831,19 @@
           <t>Error "phone must be exactly 10 digits" (API 400).</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Profile page showed 'phone must be exactly 10 digits' (element class 'msg error'). Screenshot: test-results/manual/TC-M-016.png.</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-AUTH-17)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-AUTH-17</t>
         </is>
       </c>
     </row>
@@ -1874,15 +1890,19 @@
           <t>Error "phone must be exactly 10 digits" (API 400).</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Profile page showed 'phone must be exactly 10 digits' (element class 'msg error'). Screenshot: test-results/manual/TC-M-017.png.</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-AUTH-18)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-AUTH-18</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3354,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Failed as expected behaviour is not met - Verified by script (browser check): "Added to cart" shown and badge went to 2 (cart row = qty 2). Escaped defect: the page script Int-truncates "2.5" to 2; the API itself rejects 2.5 (Postman TC-CART-05, 400). Logged as defect D-08.</t>
+          <t>Failed (re-confirmed) - manual browser run: Page message 'Added to cart'; cart badge 2, cart row qty 2 (silently truncated). Screenshot: test-results/manual/TC-M-042.png.</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
@@ -3344,7 +3364,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Browser check (Playwright, this step) + Postman: TC-CART-05 (API rejects 2.5)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-CART-05 (API rejects 2.5)</t>
         </is>
       </c>
     </row>
@@ -5033,15 +5053,19 @@
           <t>Error "card number must be exactly 16 digits" (API 400).</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Passed - manual browser run: Checkout page showed 'card number must be exactly 16 digits'; still on /checkout: True. Screenshot: test-results/manual/TC-M-071.png.</t>
+        </is>
+      </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Manual only (rule verified at API level: Postman TC-CHECK-11)</t>
+          <t>Manual browser run (Selenium, this run) + Postman: TC-CHECK-11</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6319,6 +6343,38 @@
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Postman run analysis (step 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>UI messages</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Register/Profile/Checkout messages lose their error/success colour: app.js sets class "msg error" / "msg success", while style.css styles ".msg-error" / ".msg-success", so a message shown after an API call is unstyled (text is correct, colour is lost).</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Observation / Low</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Manual browser run TC-M-016/TC-M-017 (this run)</t>
         </is>
       </c>
     </row>
@@ -6701,13 +6757,21 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Pass = verified against the live app by one of the runs above (see Actual Result). Not Run = left deliberately for the student to execute manually with screenshots; the underlying API rule is already covered by the Postman suite (see Automated By).</t>
+          <t>Pass = verified against the live app by one of the runs above (see Actual Result). All 87 cases have now been executed: 86 Pass, 1 Fail (D-08), 0 Not Run.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Manual cases (Selenium, this run)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>TC-M-004/005/007/016/017/071 executed for the first time; TC-M-042 re-checked -&gt; 6 passed, 1 known Fail (D-08 re-confirmed)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/QuickCart_Manual_Test_Cases.xlsx
+++ b/docs/QuickCart_Manual_Test_Cases.xlsx
@@ -3322,7 +3322,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Detail-page quantity as a non-integer: 2.5 - DEFECT row</t>
+          <t>Detail-page quantity as a non-integer: 2.5 (regression for D-08)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Failed (re-confirmed) - manual browser run: Page message 'Added to cart'; cart badge 2, cart row qty 2 (silently truncated). Screenshot: test-results/manual/TC-M-042.png.</t>
+          <t>Passed - manual browser run: Page message 'quantity must be an integer between 1 and 10'; cart badge 0, cart 0 rows (cart empty). Screenshot: test-results/manual/TC-M-042.png.</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Manual browser run (Selenium, this run) + Postman: TC-CART-05 (API rejects 2.5)</t>
+          <t>Manual browser run (Selenium, this run) + Selenium TC_UI_17 + Postman: TC-CART-05 (API rejects 2.5)</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed (verified in this run by TC-M-042 and TC_UI_17)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>16/16 passed (headless run)</t>
+          <t>17/17 passed (headless run)</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Pass = verified against the live app by one of the runs above (see Actual Result). All 87 cases have now been executed: 86 Pass, 1 Fail (D-08), 0 Not Run.</t>
+          <t>Pass = verified against the live app by one of the runs above (see Actual Result). All 87 cases have now been executed: 87 Pass, 0 Fail, 0 Not Run.</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>TC-M-004/005/007/016/017/071 executed for the first time; TC-M-042 re-checked -&gt; 6 passed, 1 known Fail (D-08 re-confirmed)</t>
+          <t>TC-M-004/005/007/016/017/071 executed for the first time (all Pass); TC-M-042 now Pass after the D-08 fix</t>
         </is>
       </c>
     </row>
